--- a/static/data/exports/Retro_TR_GE_2014.xlsx
+++ b/static/data/exports/Retro_TR_GE_2014.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_TR_GE_2014.xlsx
+++ b/static/data/exports/Retro_TR_GE_2014.xlsx
@@ -540,11 +540,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E2" t="n">
         <v>17931</v>
@@ -1408,11 +1408,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E16" t="n">
         <v>17827</v>
@@ -2276,11 +2276,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E30" t="n">
         <v>21396</v>
@@ -3144,11 +3144,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E44" t="n">
         <v>18330</v>
@@ -4012,11 +4012,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E58" t="n">
         <v>25011</v>
@@ -4880,11 +4880,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E72" t="n">
         <v>20922</v>
@@ -5748,11 +5748,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E86" t="n">
         <v>19709</v>
@@ -6616,11 +6616,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E100" t="n">
         <v>16390</v>
@@ -7484,11 +7484,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E114" t="n">
         <v>13262</v>
@@ -8352,11 +8352,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E128" t="n">
         <v>26306</v>
@@ -9220,11 +9220,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E142" t="n">
         <v>24207</v>
@@ -10088,11 +10088,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E156" t="n">
         <v>20363</v>
@@ -10956,11 +10956,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E170" t="n">
         <v>26987</v>
@@ -11824,11 +11824,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E184" t="n">
         <v>26102</v>
@@ -12692,11 +12692,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E198" t="n">
         <v>21136</v>
@@ -13560,11 +13560,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E212" t="n">
         <v>22722</v>
@@ -14428,11 +14428,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E226" t="n">
         <v>21056</v>
@@ -15296,11 +15296,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E240" t="n">
         <v>24420</v>
@@ -15845,20 +15845,20 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>1782850</v>
+        <v>1782851</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Partha Karmakar</t>
+          <t>Salil Saha</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>CPI(ML)(L)</t>
+          <t>AAAP</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>22936</v>
+        <v>22939</v>
       </c>
       <c r="E249" t="n">
         <v>142</v>
@@ -15882,12 +15882,12 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Partha Karmakar</t>
+          <t>Salil Saha</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>CPI(ML)(L)</t>
+          <t>AAAP</t>
         </is>
       </c>
       <c r="Q249" t="b">
@@ -15907,20 +15907,20 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>1782851</v>
+        <v>1782850</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Salil Saha</t>
+          <t>Partha Karmakar</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>AAAP</t>
+          <t>CPI(ML)(L)</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>22939</v>
+        <v>22936</v>
       </c>
       <c r="E250" t="n">
         <v>142</v>
@@ -15944,12 +15944,12 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Salil Saha</t>
+          <t>Partha Karmakar</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>AAAP</t>
+          <t>CPI(ML)(L)</t>
         </is>
       </c>
       <c r="Q250" t="b">
@@ -16164,11 +16164,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E254" t="n">
         <v>18528</v>
@@ -17032,11 +17032,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E268" t="n">
         <v>19859</v>
@@ -17900,11 +17900,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D282" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E282" t="n">
         <v>22930</v>
@@ -18768,11 +18768,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D296" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E296" t="n">
         <v>20418</v>
@@ -19636,11 +19636,11 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D310" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E310" t="n">
         <v>24435</v>
@@ -20504,11 +20504,11 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D324" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E324" t="n">
         <v>21514</v>
@@ -21310,11 +21310,11 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D337" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E337" t="n">
         <v>26382</v>
@@ -22116,11 +22116,11 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D350" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E350" t="n">
         <v>20584</v>
@@ -22603,20 +22603,20 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>1782960</v>
+        <v>1782959</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Subarna Mala Debbarma</t>
+          <t>Karna Bijoy Jamatia</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>AMB</t>
+          <t>AAAP</t>
         </is>
       </c>
       <c r="D358" t="n">
-        <v>22929</v>
+        <v>22939</v>
       </c>
       <c r="E358" t="n">
         <v>116</v>
@@ -22640,12 +22640,12 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Subarna Mala Debbarma</t>
+          <t>Karna Bijoy Jamatia</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>AMB</t>
+          <t>AAAP</t>
         </is>
       </c>
       <c r="Q358" t="b">
@@ -22665,20 +22665,20 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>1782959</v>
+        <v>1782960</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Karna Bijoy Jamatia</t>
+          <t>Subarna Mala Debbarma</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>AAAP</t>
+          <t>AMB</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>22939</v>
+        <v>22929</v>
       </c>
       <c r="E359" t="n">
         <v>116</v>
@@ -22702,12 +22702,12 @@
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>Karna Bijoy Jamatia</t>
+          <t>Subarna Mala Debbarma</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>AAAP</t>
+          <t>AMB</t>
         </is>
       </c>
       <c r="Q359" t="b">
@@ -22922,11 +22922,11 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E363" t="n">
         <v>22414</v>
@@ -23728,11 +23728,11 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D376" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E376" t="n">
         <v>20172</v>
@@ -24534,11 +24534,11 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E389" t="n">
         <v>19495</v>
@@ -25083,20 +25083,20 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>1783000</v>
+        <v>1782999</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Falguni Tripura</t>
+          <t>Basu Mog</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>CPI(ML)(L)</t>
+          <t>TPGC</t>
         </is>
       </c>
       <c r="D398" t="n">
-        <v>22936</v>
+        <v>22940</v>
       </c>
       <c r="E398" t="n">
         <v>103</v>
@@ -25120,12 +25120,12 @@
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>Falguni Tripura</t>
+          <t>Basu Mog</t>
         </is>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>CPI(ML)(L)</t>
+          <t>TPGC</t>
         </is>
       </c>
       <c r="Q398" t="b">
@@ -25145,20 +25145,20 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>1782999</v>
+        <v>1783000</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Basu Mog</t>
+          <t>Falguni Tripura</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>TPGC</t>
+          <t>CPI(ML)(L)</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>22940</v>
+        <v>22936</v>
       </c>
       <c r="E399" t="n">
         <v>103</v>
@@ -25182,12 +25182,12 @@
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>Basu Mog</t>
+          <t>Falguni Tripura</t>
         </is>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>TPGC</t>
+          <t>CPI(ML)(L)</t>
         </is>
       </c>
       <c r="Q399" t="b">
@@ -25340,11 +25340,11 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E402" t="n">
         <v>25584</v>
@@ -26208,11 +26208,11 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D416" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E416" t="n">
         <v>21354</v>
@@ -27076,11 +27076,11 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E430" t="n">
         <v>25528</v>
@@ -27944,11 +27944,11 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D444" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E444" t="n">
         <v>29538</v>
@@ -28812,11 +28812,11 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D458" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E458" t="n">
         <v>26993</v>
@@ -29680,11 +29680,11 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E472" t="n">
         <v>23765</v>
@@ -30548,11 +30548,11 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D486" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E486" t="n">
         <v>24077</v>
@@ -31416,11 +31416,11 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E500" t="n">
         <v>28238</v>
@@ -32222,11 +32222,11 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E513" t="n">
         <v>27468</v>
@@ -33028,11 +33028,11 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E526" t="n">
         <v>23550</v>
@@ -33834,11 +33834,11 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E539" t="n">
         <v>24506</v>
@@ -34640,11 +34640,11 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E552" t="n">
         <v>18265</v>
@@ -35446,11 +35446,11 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D565" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E565" t="n">
         <v>21539</v>
@@ -36252,11 +36252,11 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D578" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E578" t="n">
         <v>17634</v>
@@ -37058,11 +37058,11 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D591" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E591" t="n">
         <v>22161</v>
@@ -37864,11 +37864,11 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D604" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E604" t="n">
         <v>21716</v>
@@ -38670,11 +38670,11 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D617" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E617" t="n">
         <v>22127</v>
@@ -39095,20 +39095,20 @@
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>1783225</v>
+        <v>1783226</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Falguni Tripura</t>
+          <t>Karna Bijoy Jamatia</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>CPI(ML)(L)</t>
+          <t>AAAP</t>
         </is>
       </c>
       <c r="D624" t="n">
-        <v>22936</v>
+        <v>22939</v>
       </c>
       <c r="E624" t="n">
         <v>202</v>
@@ -39132,12 +39132,12 @@
       </c>
       <c r="K624" t="inlineStr">
         <is>
-          <t>Falguni Tripura</t>
+          <t>Karna Bijoy Jamatia</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
         <is>
-          <t>CPI(ML)(L)</t>
+          <t>AAAP</t>
         </is>
       </c>
       <c r="Q624" t="b">
@@ -39157,20 +39157,20 @@
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>1783226</v>
+        <v>1783225</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Karna Bijoy Jamatia</t>
+          <t>Falguni Tripura</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>AAAP</t>
+          <t>CPI(ML)(L)</t>
         </is>
       </c>
       <c r="D625" t="n">
-        <v>22939</v>
+        <v>22936</v>
       </c>
       <c r="E625" t="n">
         <v>202</v>
@@ -39194,12 +39194,12 @@
       </c>
       <c r="K625" t="inlineStr">
         <is>
-          <t>Karna Bijoy Jamatia</t>
+          <t>Falguni Tripura</t>
         </is>
       </c>
       <c r="L625" t="inlineStr">
         <is>
-          <t>AAAP</t>
+          <t>CPI(ML)(L)</t>
         </is>
       </c>
       <c r="Q625" t="b">
@@ -39476,11 +39476,11 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D630" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E630" t="n">
         <v>22071</v>
@@ -40282,11 +40282,11 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D643" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E643" t="n">
         <v>16073</v>
@@ -41088,11 +41088,11 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D656" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E656" t="n">
         <v>17380</v>
@@ -41894,11 +41894,11 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D669" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E669" t="n">
         <v>20569</v>
@@ -42700,11 +42700,11 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D682" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E682" t="n">
         <v>19027</v>
@@ -43506,11 +43506,11 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D695" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E695" t="n">
         <v>21659</v>
@@ -44312,11 +44312,11 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D708" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E708" t="n">
         <v>17939</v>
@@ -44613,20 +44613,20 @@
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>1783314</v>
+        <v>1783315</v>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>Karna Bijoy Jamatia</t>
+          <t>Narendra Chandra Deb Barma</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>AAAP</t>
+          <t>IPFT</t>
         </is>
       </c>
       <c r="D713" t="n">
-        <v>22939</v>
+        <v>22923</v>
       </c>
       <c r="E713" t="n">
         <v>134</v>
@@ -44650,12 +44650,12 @@
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>Karna Bijoy Jamatia</t>
+          <t>Narendra Chandra Deb Barma</t>
         </is>
       </c>
       <c r="L713" t="inlineStr">
         <is>
-          <t>AAAP</t>
+          <t>IPFT</t>
         </is>
       </c>
       <c r="Q713" t="b">
@@ -44675,20 +44675,20 @@
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>1783315</v>
+        <v>1783314</v>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Narendra Chandra Deb Barma</t>
+          <t>Karna Bijoy Jamatia</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>IPFT</t>
+          <t>AAAP</t>
         </is>
       </c>
       <c r="D714" t="n">
-        <v>22923</v>
+        <v>22939</v>
       </c>
       <c r="E714" t="n">
         <v>134</v>
@@ -44712,12 +44712,12 @@
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>Narendra Chandra Deb Barma</t>
+          <t>Karna Bijoy Jamatia</t>
         </is>
       </c>
       <c r="L714" t="inlineStr">
         <is>
-          <t>IPFT</t>
+          <t>AAAP</t>
         </is>
       </c>
       <c r="Q714" t="b">
@@ -45118,11 +45118,11 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D721" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E721" t="n">
         <v>17796</v>
@@ -45924,11 +45924,11 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D734" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E734" t="n">
         <v>17678</v>
@@ -46730,11 +46730,11 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D747" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E747" t="n">
         <v>16678</v>
@@ -47155,20 +47155,20 @@
     </row>
     <row r="754">
       <c r="A754" t="n">
-        <v>1783356</v>
+        <v>1783355</v>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Narendra Chandra Deb Barma</t>
+          <t>Basu Mog</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>IPFT</t>
+          <t>TPGC</t>
         </is>
       </c>
       <c r="D754" t="n">
-        <v>22923</v>
+        <v>22940</v>
       </c>
       <c r="E754" t="n">
         <v>79</v>
@@ -47192,12 +47192,12 @@
       </c>
       <c r="K754" t="inlineStr">
         <is>
-          <t>Narendra Chandra Deb Barma</t>
+          <t>Basu Mog</t>
         </is>
       </c>
       <c r="L754" t="inlineStr">
         <is>
-          <t>IPFT</t>
+          <t>TPGC</t>
         </is>
       </c>
       <c r="Q754" t="b">
@@ -47217,20 +47217,20 @@
     </row>
     <row r="755">
       <c r="A755" t="n">
-        <v>1783355</v>
+        <v>1783356</v>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Basu Mog</t>
+          <t>Narendra Chandra Deb Barma</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>TPGC</t>
+          <t>IPFT</t>
         </is>
       </c>
       <c r="D755" t="n">
-        <v>22940</v>
+        <v>22923</v>
       </c>
       <c r="E755" t="n">
         <v>79</v>
@@ -47254,12 +47254,12 @@
       </c>
       <c r="K755" t="inlineStr">
         <is>
-          <t>Basu Mog</t>
+          <t>Narendra Chandra Deb Barma</t>
         </is>
       </c>
       <c r="L755" t="inlineStr">
         <is>
-          <t>TPGC</t>
+          <t>IPFT</t>
         </is>
       </c>
       <c r="Q755" t="b">
@@ -47536,11 +47536,11 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D760" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E760" t="n">
         <v>19537</v>
@@ -48342,11 +48342,11 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D773" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E773" t="n">
         <v>17969</v>
@@ -49148,11 +49148,11 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D786" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E786" t="n">
         <v>19388</v>
@@ -49954,11 +49954,11 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D799" t="n">
-        <v>22930</v>
+        <v>22922</v>
       </c>
       <c r="E799" t="n">
         <v>18722</v>
